--- a/site/ADP-Workforce-Now-to-SQL-Server-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-SQL-Server-Integration-Guide/headings.xlsx
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Manage Identity Warehouse</t>
+          <t>Data Mapping</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
